--- a/docs/ImmunizationReaction.xlsx
+++ b/docs/ImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -82,7 +82,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t xml:space="preserve">Terminology Maps ImmunizationReaction </t>
+    <t>Terminology Maps ImmunizationReaction</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/ImmunizationReaction.xlsx
+++ b/docs/ImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ImmunizationReaction.xlsx
+++ b/docs/ImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ImmunizationReaction.xlsx
+++ b/docs/ImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ImmunizationReaction.xlsx
+++ b/docs/ImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ImmunizationReaction.xlsx
+++ b/docs/ImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ImmunizationReaction.xlsx
+++ b/docs/ImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ImmunizationReaction.xlsx
+++ b/docs/ImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ImmunizationReaction.xlsx
+++ b/docs/ImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
